--- a/output/graficos_nacionales/plot_nacional_regiones_i_ingr_mean_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_ingr_mean_a_2019.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:16</t>
+    <t xml:space="preserve">2026-09-09 21:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_i_ingr_mean_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_ingr_mean_a_2019.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:01</t>
+    <t xml:space="preserve">2026-09-17 13:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_i_ingr_mean_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_ingr_mean_a_2019.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:49</t>
+    <t xml:space="preserve">2026-10-05 18:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -594,7 +594,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>339910.12</v>
+        <v>339910.13</v>
       </c>
     </row>
     <row r="16">
